--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU10/HRM/post DFS_HRM-2031-0220/Panel-28/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU10_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU10/HRM/post DFS_HRM-2031-0220/Panel-28/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU10_Back_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,26 +456,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Pad 1</t>
+          <t>Pad Pos 1</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.79965</v>
+        <v>17.48031</v>
       </c>
       <c r="D2" t="n">
-        <v>17.57176</v>
+        <v>17.38073</v>
       </c>
       <c r="E2" t="n">
-        <v>17.63025</v>
+        <v>17.39073</v>
       </c>
       <c r="F2" t="n">
-        <v>45.16181</v>
+        <v>44.62868</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05228</v>
+        <v>0.05238</v>
       </c>
       <c r="H2" t="n">
-        <v>1.89532</v>
+        <v>1.91715</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.45823</v>
+        <v>17.65634</v>
       </c>
       <c r="D3" t="n">
-        <v>17.52238</v>
+        <v>17.21005</v>
       </c>
       <c r="E3" t="n">
-        <v>17.05304</v>
+        <v>17.42332</v>
       </c>
       <c r="F3" t="n">
-        <v>44.48214</v>
+        <v>44.63859</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05239</v>
+        <v>0.05284</v>
       </c>
       <c r="H3" t="n">
-        <v>1.91458</v>
+        <v>1.89637</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.39702</v>
+        <v>17.26453</v>
       </c>
       <c r="D4" t="n">
-        <v>17.48504</v>
+        <v>17.19204</v>
       </c>
       <c r="E4" t="n">
-        <v>17.41335</v>
+        <v>17.24706</v>
       </c>
       <c r="F4" t="n">
-        <v>44.54445</v>
+        <v>43.71499</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05441</v>
+        <v>0.05387</v>
       </c>
       <c r="H4" t="n">
-        <v>1.89089</v>
+        <v>1.87804</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>17.75323</v>
+        <v>17.8355</v>
       </c>
       <c r="D5" t="n">
-        <v>17.36269</v>
+        <v>17.43113</v>
       </c>
       <c r="E5" t="n">
-        <v>17.19844</v>
+        <v>17.46849</v>
       </c>
       <c r="F5" t="n">
-        <v>44.65764</v>
+        <v>43.8499</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05341</v>
+        <v>0.05311</v>
       </c>
       <c r="H5" t="n">
-        <v>1.91151</v>
+        <v>1.92841</v>
       </c>
     </row>
     <row r="6">
@@ -560,22 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.22929</v>
+        <v>17.592</v>
       </c>
       <c r="D6" t="n">
-        <v>17.45737</v>
+        <v>17.26043</v>
       </c>
       <c r="E6" t="n">
-        <v>17.58648</v>
+        <v>17.43231</v>
       </c>
       <c r="F6" t="n">
-        <v>43.73746</v>
+        <v>44.44436</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0537</v>
+        <v>0.05365</v>
       </c>
       <c r="H6" t="n">
-        <v>1.91447</v>
+        <v>1.90942</v>
       </c>
     </row>
     <row r="7">
@@ -585,22 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.42833</v>
+        <v>17.76527</v>
       </c>
       <c r="D7" t="n">
-        <v>17.14986</v>
+        <v>17.15842</v>
       </c>
       <c r="E7" t="n">
-        <v>17.79362</v>
+        <v>17.71609</v>
       </c>
       <c r="F7" t="n">
-        <v>45.0034</v>
+        <v>44.10858</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05303</v>
+        <v>0.05304</v>
       </c>
       <c r="H7" t="n">
-        <v>1.92281</v>
+        <v>1.88202</v>
       </c>
     </row>
     <row r="8">
@@ -610,22 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.6302</v>
+        <v>18.14803</v>
       </c>
       <c r="D8" t="n">
-        <v>17.61752</v>
+        <v>17.31122</v>
       </c>
       <c r="E8" t="n">
-        <v>17.43078</v>
+        <v>17.35207</v>
       </c>
       <c r="F8" t="n">
-        <v>44.76483</v>
+        <v>44.82245</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05292</v>
+        <v>0.05317</v>
       </c>
       <c r="H8" t="n">
-        <v>1.90389</v>
+        <v>1.90079</v>
       </c>
     </row>
     <row r="9">
@@ -635,22 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17.65251</v>
+        <v>17.72986</v>
       </c>
       <c r="D9" t="n">
-        <v>17.39942</v>
+        <v>17.48047</v>
       </c>
       <c r="E9" t="n">
-        <v>17.3795</v>
+        <v>17.53658</v>
       </c>
       <c r="F9" t="n">
-        <v>44.94225</v>
+        <v>44.86352</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05335</v>
+        <v>0.05162</v>
       </c>
       <c r="H9" t="n">
-        <v>1.87976</v>
+        <v>1.88095</v>
       </c>
     </row>
     <row r="10">
@@ -660,22 +660,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17.79609</v>
+        <v>17.60746</v>
       </c>
       <c r="D10" t="n">
-        <v>16.94888</v>
+        <v>17.30278</v>
       </c>
       <c r="E10" t="n">
-        <v>17.73749</v>
+        <v>17.44225</v>
       </c>
       <c r="F10" t="n">
-        <v>44.87699</v>
+        <v>43.89339</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05238</v>
+        <v>0.05159</v>
       </c>
       <c r="H10" t="n">
-        <v>1.91244</v>
+        <v>1.87476</v>
       </c>
     </row>
     <row r="11">
@@ -718,26 +718,26 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Pad 1</t>
+          <t>Pad Pos 2</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>17.3144</v>
+        <v>17.79886</v>
       </c>
       <c r="D12" t="n">
-        <v>17.2094</v>
+        <v>17.25082</v>
       </c>
       <c r="E12" t="n">
-        <v>17.25217</v>
+        <v>17.29085</v>
       </c>
       <c r="F12" t="n">
-        <v>44.26309</v>
+        <v>44.86365</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0537</v>
+        <v>0.05307</v>
       </c>
       <c r="H12" t="n">
-        <v>1.91363</v>
+        <v>1.90181</v>
       </c>
     </row>
     <row r="13">
@@ -747,22 +747,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>17.37298</v>
+        <v>17.50498</v>
       </c>
       <c r="D13" t="n">
-        <v>17.3886</v>
+        <v>16.97203</v>
       </c>
       <c r="E13" t="n">
-        <v>17.43822</v>
+        <v>17.30954</v>
       </c>
       <c r="F13" t="n">
-        <v>45.59486</v>
+        <v>44.51577</v>
       </c>
       <c r="G13" t="n">
-        <v>0.05251</v>
+        <v>0.05294</v>
       </c>
       <c r="H13" t="n">
-        <v>1.91293</v>
+        <v>1.89504</v>
       </c>
     </row>
     <row r="14">
@@ -772,22 +772,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>17.80666</v>
+        <v>17.68403</v>
       </c>
       <c r="D14" t="n">
-        <v>17.06521</v>
+        <v>17.25099</v>
       </c>
       <c r="E14" t="n">
-        <v>17.47954</v>
+        <v>17.53124</v>
       </c>
       <c r="F14" t="n">
-        <v>43.93067</v>
+        <v>45.18584</v>
       </c>
       <c r="G14" t="n">
-        <v>0.05304</v>
+        <v>0.0524</v>
       </c>
       <c r="H14" t="n">
-        <v>1.91662</v>
+        <v>1.90396</v>
       </c>
     </row>
     <row r="15">
@@ -797,22 +797,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>17.55126</v>
+        <v>17.45839</v>
       </c>
       <c r="D15" t="n">
-        <v>17.46732</v>
+        <v>17.23947</v>
       </c>
       <c r="E15" t="n">
-        <v>17.58329</v>
+        <v>17.34584</v>
       </c>
       <c r="F15" t="n">
-        <v>44.41597</v>
+        <v>44.11409</v>
       </c>
       <c r="G15" t="n">
-        <v>0.05391</v>
+        <v>0.05376</v>
       </c>
       <c r="H15" t="n">
-        <v>1.89295</v>
+        <v>1.88238</v>
       </c>
     </row>
     <row r="16">
@@ -822,22 +822,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>17.18454</v>
+        <v>17.84307</v>
       </c>
       <c r="D16" t="n">
-        <v>17.69983</v>
+        <v>17.00783</v>
       </c>
       <c r="E16" t="n">
-        <v>17.60579</v>
+        <v>17.72381</v>
       </c>
       <c r="F16" t="n">
-        <v>44.08571</v>
+        <v>43.64652</v>
       </c>
       <c r="G16" t="n">
-        <v>0.05333</v>
+        <v>0.05304</v>
       </c>
       <c r="H16" t="n">
-        <v>1.88866</v>
+        <v>1.96307</v>
       </c>
     </row>
     <row r="17">
@@ -847,22 +847,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>17.34551</v>
+        <v>17.6714</v>
       </c>
       <c r="D17" t="n">
-        <v>17.21729</v>
+        <v>17.20963</v>
       </c>
       <c r="E17" t="n">
-        <v>17.44263</v>
+        <v>17.47145</v>
       </c>
       <c r="F17" t="n">
-        <v>45.09512</v>
+        <v>45.0809</v>
       </c>
       <c r="G17" t="n">
-        <v>0.05249</v>
+        <v>0.05299</v>
       </c>
       <c r="H17" t="n">
-        <v>1.86241</v>
+        <v>1.84811</v>
       </c>
     </row>
     <row r="18">
@@ -872,22 +872,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>17.31996</v>
+        <v>17.85726</v>
       </c>
       <c r="D18" t="n">
-        <v>17.5164</v>
+        <v>17.61058</v>
       </c>
       <c r="E18" t="n">
-        <v>17.30744</v>
+        <v>17.62485</v>
       </c>
       <c r="F18" t="n">
-        <v>44.68263</v>
+        <v>44.81024</v>
       </c>
       <c r="G18" t="n">
         <v>0.05324</v>
       </c>
       <c r="H18" t="n">
-        <v>1.88669</v>
+        <v>1.88168</v>
       </c>
     </row>
     <row r="19">
@@ -897,22 +897,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>17.4561</v>
+        <v>17.67863</v>
       </c>
       <c r="D19" t="n">
-        <v>17.3628</v>
+        <v>16.95118</v>
       </c>
       <c r="E19" t="n">
-        <v>17.58228</v>
+        <v>17.53948</v>
       </c>
       <c r="F19" t="n">
-        <v>44.65058</v>
+        <v>44.24909</v>
       </c>
       <c r="G19" t="n">
-        <v>0.05374</v>
+        <v>0.0529</v>
       </c>
       <c r="H19" t="n">
-        <v>1.8963</v>
+        <v>1.96425</v>
       </c>
     </row>
     <row r="20">
@@ -922,33 +922,43 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>17.62418</v>
+        <v>17.63627</v>
       </c>
       <c r="D20" t="n">
-        <v>17.21442</v>
+        <v>17.33363</v>
       </c>
       <c r="E20" t="n">
-        <v>17.27404</v>
+        <v>17.55954</v>
       </c>
       <c r="F20" t="n">
-        <v>44.35305</v>
+        <v>44.56369</v>
       </c>
       <c r="G20" t="n">
-        <v>0.05191</v>
+        <v>0.054</v>
       </c>
       <c r="H20" t="n">
-        <v>1.90378</v>
+        <v>1.8741</v>
       </c>
     </row>
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>Dimple</t>
+          <t>Max Stepheight</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Bump</t>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Radius</t>
         </is>
       </c>
     </row>
@@ -960,14 +970,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>via 1</t>
+          <t>SR Pad Pos 1</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.63609</v>
+        <v>16.58188</v>
       </c>
       <c r="D22" t="n">
-        <v>1.15751</v>
+        <v>16.04057</v>
+      </c>
+      <c r="E22" t="n">
+        <v>16.21352</v>
+      </c>
+      <c r="F22" t="n">
+        <v>269.51353</v>
       </c>
     </row>
     <row r="23">
@@ -977,10 +993,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.63131</v>
+        <v>16.49559</v>
       </c>
       <c r="D23" t="n">
-        <v>1.16673</v>
+        <v>16.17113</v>
+      </c>
+      <c r="E23" t="n">
+        <v>16.49193</v>
+      </c>
+      <c r="F23" t="n">
+        <v>264.03904</v>
       </c>
     </row>
     <row r="24">
@@ -990,10 +1012,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.6454299999999999</v>
+        <v>16.49918</v>
       </c>
       <c r="D24" t="n">
-        <v>1.16623</v>
+        <v>16.37628</v>
+      </c>
+      <c r="E24" t="n">
+        <v>16.37826</v>
+      </c>
+      <c r="F24" t="n">
+        <v>267.82307</v>
       </c>
     </row>
     <row r="25">
@@ -1003,10 +1031,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.64088</v>
+        <v>16.47062</v>
       </c>
       <c r="D25" t="n">
-        <v>1.16871</v>
+        <v>16.38533</v>
+      </c>
+      <c r="E25" t="n">
+        <v>16.44905</v>
+      </c>
+      <c r="F25" t="n">
+        <v>262.31963</v>
       </c>
     </row>
     <row r="26">
@@ -1016,10 +1050,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.63587</v>
+        <v>16.59614</v>
       </c>
       <c r="D26" t="n">
-        <v>1.16506</v>
+        <v>16.27864</v>
+      </c>
+      <c r="E26" t="n">
+        <v>16.31899</v>
+      </c>
+      <c r="F26" t="n">
+        <v>268.73528</v>
       </c>
     </row>
     <row r="27">
@@ -1029,10 +1069,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.65105</v>
+        <v>16.55258</v>
       </c>
       <c r="D27" t="n">
-        <v>1.17452</v>
+        <v>16.13066</v>
+      </c>
+      <c r="E27" t="n">
+        <v>16.52178</v>
+      </c>
+      <c r="F27" t="n">
+        <v>266.74713</v>
       </c>
     </row>
     <row r="28">
@@ -1042,10 +1088,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.63413</v>
+        <v>16.53748</v>
       </c>
       <c r="D28" t="n">
-        <v>1.16917</v>
+        <v>16.36472</v>
+      </c>
+      <c r="E28" t="n">
+        <v>16.4168</v>
+      </c>
+      <c r="F28" t="n">
+        <v>262.51236</v>
       </c>
     </row>
     <row r="29">
@@ -1055,10 +1107,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.62779</v>
+        <v>16.49056</v>
       </c>
       <c r="D29" t="n">
-        <v>1.20083</v>
+        <v>16.20063</v>
+      </c>
+      <c r="E29" t="n">
+        <v>16.23088</v>
+      </c>
+      <c r="F29" t="n">
+        <v>266.97532</v>
       </c>
     </row>
     <row r="30">
@@ -1068,10 +1126,578 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.64499</v>
+        <v>16.49311</v>
       </c>
       <c r="D30" t="n">
-        <v>1.1562</v>
+        <v>16.24388</v>
+      </c>
+      <c r="E30" t="n">
+        <v>16.25417</v>
+      </c>
+      <c r="F30" t="n">
+        <v>269.66974</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Trace Pos 1</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>17.49718</v>
+      </c>
+      <c r="D32" t="n">
+        <v>16.65534</v>
+      </c>
+      <c r="E32" t="n">
+        <v>17.36954</v>
+      </c>
+      <c r="F32" t="n">
+        <v>22.45986</v>
+      </c>
+      <c r="G32" t="n">
+        <v>35.08718</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>17.19376</v>
+      </c>
+      <c r="D33" t="n">
+        <v>16.62395</v>
+      </c>
+      <c r="E33" t="n">
+        <v>16.8894</v>
+      </c>
+      <c r="F33" t="n">
+        <v>23.24744</v>
+      </c>
+      <c r="G33" t="n">
+        <v>36.71308</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>17.5458</v>
+      </c>
+      <c r="D34" t="n">
+        <v>16.79967</v>
+      </c>
+      <c r="E34" t="n">
+        <v>17.3095</v>
+      </c>
+      <c r="F34" t="n">
+        <v>22.84141</v>
+      </c>
+      <c r="G34" t="n">
+        <v>35.6247</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>17.60679</v>
+      </c>
+      <c r="D35" t="n">
+        <v>16.91438</v>
+      </c>
+      <c r="E35" t="n">
+        <v>17.02214</v>
+      </c>
+      <c r="F35" t="n">
+        <v>23.09662</v>
+      </c>
+      <c r="G35" t="n">
+        <v>36.43618</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>17.50127</v>
+      </c>
+      <c r="D36" t="n">
+        <v>17.02816</v>
+      </c>
+      <c r="E36" t="n">
+        <v>17.40259</v>
+      </c>
+      <c r="F36" t="n">
+        <v>22.59526</v>
+      </c>
+      <c r="G36" t="n">
+        <v>35.51418</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>17.6147</v>
+      </c>
+      <c r="D37" t="n">
+        <v>16.79817</v>
+      </c>
+      <c r="E37" t="n">
+        <v>17.03536</v>
+      </c>
+      <c r="F37" t="n">
+        <v>22.94156</v>
+      </c>
+      <c r="G37" t="n">
+        <v>34.92667</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>17.2174</v>
+      </c>
+      <c r="D38" t="n">
+        <v>16.52498</v>
+      </c>
+      <c r="E38" t="n">
+        <v>16.87129</v>
+      </c>
+      <c r="F38" t="n">
+        <v>22.54453</v>
+      </c>
+      <c r="G38" t="n">
+        <v>35.28676</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>17.45455</v>
+      </c>
+      <c r="D39" t="n">
+        <v>16.54838</v>
+      </c>
+      <c r="E39" t="n">
+        <v>17.21847</v>
+      </c>
+      <c r="F39" t="n">
+        <v>22.69054</v>
+      </c>
+      <c r="G39" t="n">
+        <v>36.62696</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>17.97777</v>
+      </c>
+      <c r="D40" t="n">
+        <v>16.6077</v>
+      </c>
+      <c r="E40" t="n">
+        <v>17.2291</v>
+      </c>
+      <c r="F40" t="n">
+        <v>22.98804</v>
+      </c>
+      <c r="G40" t="n">
+        <v>35.87054</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Via Pos 1</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0.64106</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1.17454</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0.6389</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1.15192</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0.64293</v>
+      </c>
+      <c r="D44" t="n">
+        <v>1.2038</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0.65237</v>
+      </c>
+      <c r="D45" t="n">
+        <v>1.16785</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0.65389</v>
+      </c>
+      <c r="D46" t="n">
+        <v>1.15004</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0.63532</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1.17743</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>0.62943</v>
+      </c>
+      <c r="D48" t="n">
+        <v>1.1776</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>0.64897</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1.18155</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>0.63215</v>
+      </c>
+      <c r="D50" t="n">
+        <v>1.17256</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Radius</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Landing Pad 1</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>17.96122</v>
+      </c>
+      <c r="D52" t="n">
+        <v>17.28033</v>
+      </c>
+      <c r="E52" t="n">
+        <v>17.73049</v>
+      </c>
+      <c r="F52" t="n">
+        <v>44.41215</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>17.58312</v>
+      </c>
+      <c r="D53" t="n">
+        <v>17.19482</v>
+      </c>
+      <c r="E53" t="n">
+        <v>17.43338</v>
+      </c>
+      <c r="F53" t="n">
+        <v>44.28206</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>17.80978</v>
+      </c>
+      <c r="D54" t="n">
+        <v>17.59544</v>
+      </c>
+      <c r="E54" t="n">
+        <v>17.71874</v>
+      </c>
+      <c r="F54" t="n">
+        <v>44.13633</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>17.80098</v>
+      </c>
+      <c r="D55" t="n">
+        <v>17.21374</v>
+      </c>
+      <c r="E55" t="n">
+        <v>17.21892</v>
+      </c>
+      <c r="F55" t="n">
+        <v>44.96547</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>17.69382</v>
+      </c>
+      <c r="D56" t="n">
+        <v>17.253</v>
+      </c>
+      <c r="E56" t="n">
+        <v>17.45008</v>
+      </c>
+      <c r="F56" t="n">
+        <v>44.56493</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>17.89011</v>
+      </c>
+      <c r="D57" t="n">
+        <v>17.29738</v>
+      </c>
+      <c r="E57" t="n">
+        <v>17.60006</v>
+      </c>
+      <c r="F57" t="n">
+        <v>45.18769</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>17.72835</v>
+      </c>
+      <c r="D58" t="n">
+        <v>17.34892</v>
+      </c>
+      <c r="E58" t="n">
+        <v>17.51701</v>
+      </c>
+      <c r="F58" t="n">
+        <v>44.78916</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>17.52335</v>
+      </c>
+      <c r="D59" t="n">
+        <v>17.27154</v>
+      </c>
+      <c r="E59" t="n">
+        <v>17.46412</v>
+      </c>
+      <c r="F59" t="n">
+        <v>44.36974</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>17.68433</v>
+      </c>
+      <c r="D60" t="n">
+        <v>17.11611</v>
+      </c>
+      <c r="E60" t="n">
+        <v>17.56223</v>
+      </c>
+      <c r="F60" t="n">
+        <v>44.33024</v>
       </c>
     </row>
   </sheetData>
